--- a/survey_templates/035_makeup_survey--survey_templates.xlsx
+++ b/survey_templates/035_makeup_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mac'}</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mac'}</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'estee_lauder'}</t>
+          <t>estee_lauder</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Estee Lauder'}</t>
+          <t>Estee Lauder</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_"l'oreal"}</t>
+          <t>l'oreal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': "L'Oreal"}</t>
+          <t>L'Oreal</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning_routine'}</t>
+          <t>morning_routine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning routine'}</t>
+          <t>Morning routine</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'night_time'}</t>
+          <t>night_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Night time'}</t>
+          <t>Night time</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'foundation'}</t>
+          <t>foundation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Foundation'}</t>
+          <t>Foundation</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mascara'}</t>
+          <t>mascara</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mascara'}</t>
+          <t>Mascara</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'powder'}</t>
+          <t>powder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Powder'}</t>
+          <t>Powder</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pink'}</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pink'}</t>
+          <t>Pink</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
